--- a/esyluban/templates/DataTables/items.xlsx
+++ b/esyluban/templates/DataTables/items.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string#ref=text.TbText</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string#ref=text.TbText</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>木剑</t>
+          <t>/item_1001_name</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -496,7 +496,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>新手用的练习剑</t>
+          <t>/item_1001_desc</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>铁剑</t>
+          <t>/item_1002_name</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -514,7 +514,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>standard iron sword</t>
+          <t>/item_1002_desc</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>治疗药水</t>
+          <t>/item_1003_name</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -532,7 +532,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>恢复少量生命</t>
+          <t>/item_1003_desc</t>
         </is>
       </c>
     </row>
